--- a/technology_surveys/017_tech_gadget_usability_survey--technology_surveys.xlsx
+++ b/technology_surveys/017_tech_gadget_usability_survey--technology_surveys.xlsx
@@ -1,14 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="settings" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -31,7 +32,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -42,6 +43,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="004472C4"/>
         <bgColor rgb="004472C4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0070AD47"/>
+        <bgColor rgb="0070AD47"/>
       </patternFill>
     </fill>
   </fills>
@@ -57,9 +64,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -427,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E32"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="7" customWidth="1" min="1" max="1"/>
-    <col width="48" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -510,12 +520,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>tech_gadget_usability_survey_form</t>
+          <t>usage_frequency</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>main</t>
+          <t>How long do you use the tech gadget daily?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -533,35 +543,35 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>user_info</t>
+          <t>user_experience</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>user_info</t>
+          <t>Rate the user experience of the tech gadget</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>product_info</t>
+          <t>favorite_features</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>product_info</t>
+          <t>Which features do you enjoy most about the tech gadget?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -574,23 +584,23 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>tech_gadget_usability_survey_form_questions_1</t>
+          <t>likelihood_to_recommend</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>main</t>
+          <t>How likely are you to recommend the tech gadget to a friend?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -602,12 +612,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>tech_gadget_usability_survey_form_questions_2</t>
+          <t>work_use</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>main</t>
+          <t>How often do you use the tech gadget for work?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -625,35 +635,35 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>tech_gadget_usability_survey_form_questions_3</t>
+          <t>performance</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>main</t>
+          <t>How satisfied are you with the tech gadget's performance?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>tech_gadget_usability_survey_form_questions_4</t>
+          <t>suggestions</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>main</t>
+          <t>Do you have any suggestions for improving the tech gadget's usability?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -671,12 +681,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>tech_gadget_usability_survey_form_questions_5</t>
+          <t>battery_importance</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>main</t>
+          <t>How important is the battery life of the tech gadget to you?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -694,18 +704,18 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>tech_gadget_usability_survey_form_questions_6</t>
+          <t>design_aesthetic</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>main</t>
+          <t>How would you rate the tech gadget's design aesthetic?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -717,35 +727,35 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>tech_gadget_usability_survey_form_questions_7</t>
+          <t>navigation</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>main</t>
+          <t>How easy is it to navigate the tech gadget's interface?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>tech_gadget_usability_survey_form_questions_8</t>
+          <t>software_issues</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>main</t>
+          <t>Have you ever experienced any issues with the tech gadget's software or hardware?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -763,12 +773,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>tech_gadget_usability_survey_form_questions_9</t>
+          <t>price</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>main</t>
+          <t>Would you pay more for a tech gadget with better performance?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -786,12 +796,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>tech_gadget_usability_survey_form_questions_10</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>main</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -804,366 +814,21 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>tech_gadget_usability_survey_form_questions_11</t>
+          <t>note</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>main</t>
+          <t>Additional comments or feedback</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>tech_gadget_usability_survey_form_questions_12</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>main</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>tech_gadget_usability_survey_form_questions_13</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>main</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>tech_gadget_usability_survey_form_questions_14</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>main</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>tech_gadget_usability_survey_form_questions_15</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>main</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>tech_gadget_usability_survey_form_questions_16</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>main</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>tech_gadget_usability_survey_form_questions_17</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>main</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>tech_gadget_usability_survey_form_questions_18</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>main</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>tech_gadget_usability_survey_form_questions_19</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>main</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>tech_gadget_usability_survey_form_questions_20</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>main</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>tech_gadget_usability_survey_form_questions_21</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>main</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>tech_gadget_usability_survey_form_questions_22</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>main</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>submission</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>submit</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>phone_number</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>phone_number</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1175,6 +840,212 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="33" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>list_name</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>label</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>favorite_features_choices</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>performance</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>favorite_features_choices</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>design</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>favorite_features_choices</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>user_interface</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>User Interface</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>favorite_features_choices</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>other_(please_specify)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Other (please specify)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>likelihood_to_recommend_choices</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>very_likely</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Very likely</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>likelihood_to_recommend_choices</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>somewhat_likely</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Somewhat likely</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>likelihood_to_recommend_choices</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>not_very_likely</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Not very likely</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>likelihood_to_recommend_choices</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>not_at_all</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Not at all</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>software_issues_choices</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>software_issues_choices</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
